--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3261</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3262</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="11">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3261</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1704</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1556</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1432</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="9">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Chiffchaff</t>
+          <t>Pied Wagtail</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -763,11 +763,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Pied Wagtail</t>
+          <t>Chiffchaff</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3267</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="8">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14">

--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Birds/composition.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="9">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28">
@@ -823,7 +823,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Long-Tailed Tit</t>
+          <t>Mute Swan</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -833,11 +833,11 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Mute Swan</t>
+          <t>Long-Tailed Tit</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42">
